--- a/data/economie/Data_Salaires_Prix.xlsx
+++ b/data/economie/Data_Salaires_Prix.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t xml:space="preserve">Indicateur</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t xml:space="preserve">Salaire_median_indice_base100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smic_eur_heure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salaire_median_eur_an</t>
   </si>
   <si>
     <t xml:space="preserve">Base 1990 = 100 pour les 3 séries. Voir Indicateurs_ref.</t>
@@ -229,8 +235,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -242,11 +252,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -505,127 +519,127 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="62"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>27</v>
       </c>
     </row>
@@ -645,521 +659,739 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="E1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="n">
         <v>1990</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="E2" s="5" t="n">
+        <v>4.8692</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>13164</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="n">
         <v>1991</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="4" t="n">
         <v>102.3</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>103.1</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>103.7</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="E3" s="5" t="n">
+        <v>4.979</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>13648</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
         <v>1992</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="4" t="n">
         <v>106.6</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>105.6</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>106.9</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="E4" s="5" t="n">
+        <v>5.1924</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>14072</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
         <v>1993</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="4" t="n">
         <v>109</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>107.9</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>109.6</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="E5" s="5" t="n">
+        <v>5.3098</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>14423</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
         <v>1994</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="4" t="n">
         <v>111.3</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>109.6</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>109.7</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="E6" s="5" t="n">
+        <v>5.4211</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>14446</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
         <v>1995</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="4" t="n">
         <v>115.8</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>111.7</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>112.9</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+      <c r="E7" s="5" t="n">
+        <v>5.6376</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>14866</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
         <v>1996</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="4" t="n">
         <v>118.7</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>113.9</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>115.1</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+      <c r="E8" s="5" t="n">
+        <v>5.7793</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>15146</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
         <v>1997</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="4" t="n">
         <v>123.5</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>115.1</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>117.6</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+      <c r="E9" s="5" t="n">
+        <v>6.0111</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>15479</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
         <v>1998</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="4" t="n">
         <v>125.9</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="4" t="n">
         <v>115.8</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>119.8</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+      <c r="E10" s="5" t="n">
+        <v>6.1315</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>15765</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
         <v>1999</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="4" t="n">
         <v>127.5</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="4" t="n">
         <v>116.6</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>121.4</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+      <c r="E11" s="5" t="n">
+        <v>6.2077</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>15980</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="4" t="n">
         <v>131.6</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>118.6</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>123.3</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+      <c r="E12" s="5" t="n">
+        <v>6.4059</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>16237</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
         <v>2001</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="4" t="n">
         <v>137</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="4" t="n">
         <v>120.5</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>124.8</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+      <c r="E13" s="5" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>16432</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
         <v>2002</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="4" t="n">
         <v>140.3</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="4" t="n">
         <v>122.8</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>128.1</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+      <c r="E14" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>16866</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
         <v>2003</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="4" t="n">
         <v>147.7</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>125.5</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>130.6</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+      <c r="E15" s="5" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>17196</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
         <v>2004</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="4" t="n">
         <v>156.3</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="4" t="n">
         <v>128.1</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>133</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+      <c r="E16" s="5" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>17506</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
         <v>2005</v>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="4" t="n">
         <v>164.9</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="4" t="n">
         <v>130.4</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <v>137</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+      <c r="E17" s="5" t="n">
+        <v>8.03</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>18036</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
         <v>2006</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="4" t="n">
         <v>169.8</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="4" t="n">
         <v>132.4</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <v>139</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
+      <c r="E18" s="5" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>18292</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
         <v>2007</v>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="4" t="n">
         <v>173.3</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="4" t="n">
         <v>134.6</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="4" t="n">
         <v>142.7</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
+      <c r="E19" s="5" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>18781</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
         <v>2008</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="4" t="n">
         <v>178.9</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="4" t="n">
         <v>138.2</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>147.8</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="n">
+      <c r="E20" s="5" t="n">
+        <v>8.71</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>19455</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
         <v>2009</v>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="4" t="n">
         <v>181.1</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="4" t="n">
         <v>138.3</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="4" t="n">
         <v>151</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="n">
+      <c r="E21" s="5" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>19876</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
         <v>2010</v>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="4" t="n">
         <v>182</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="4" t="n">
         <v>140.5</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="4" t="n">
         <v>153.9</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="n">
+      <c r="E22" s="5" t="n">
+        <v>8.86</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>20255</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
         <v>2011</v>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="4" t="n">
         <v>188.7</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="4" t="n">
         <v>143.6</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="4" t="n">
         <v>157.2</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="n">
+      <c r="E23" s="5" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>20700</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
         <v>2012</v>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="4" t="n">
         <v>193.1</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="4" t="n">
         <v>146.3</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="4" t="n">
         <v>159.3</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="n">
+      <c r="E24" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>20973</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
         <v>2013</v>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="4" t="n">
         <v>193.7</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="4" t="n">
         <v>147.6</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="4" t="n">
         <v>160.7</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="n">
+      <c r="E25" s="5" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>21152</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
         <v>2014</v>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="4" t="n">
         <v>195.7</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="4" t="n">
         <v>148.1</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>161.5</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="n">
+      <c r="E26" s="5" t="n">
+        <v>9.53</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>21255</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="4" t="n">
         <v>197.4</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C27" s="4" t="n">
         <v>148.3</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="4" t="n">
         <v>162.7</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="n">
+      <c r="E27" s="5" t="n">
+        <v>9.61</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>21415</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
         <v>2016</v>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="4" t="n">
         <v>198.6</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="4" t="n">
         <v>148.6</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="4" t="n">
         <v>163.7</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="n">
+      <c r="E28" s="5" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>21548</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
         <v>2017</v>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="4" t="n">
         <v>200.4</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="4" t="n">
         <v>151.1</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="4" t="n">
         <v>167.6</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="n">
+      <c r="E29" s="5" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>22069</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
         <v>2018</v>
       </c>
-      <c r="B30" s="3" t="n">
+      <c r="B30" s="4" t="n">
         <v>202.9</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="4" t="n">
         <v>153.8</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="4" t="n">
         <v>171.2</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="n">
+      <c r="E30" s="5" t="n">
+        <v>9.88</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>22538</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
         <v>2019</v>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B31" s="4" t="n">
         <v>206</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="4" t="n">
         <v>155.6</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="4" t="n">
         <v>176.7</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="n">
+      <c r="E31" s="5" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>23257</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
         <v>2020</v>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="4" t="n">
         <v>208.5</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="4" t="n">
         <v>156</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="4" t="n">
         <v>168.6</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="n">
+      <c r="E32" s="5" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>22188</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
         <v>2021</v>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="4" t="n">
         <v>215.2</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="4" t="n">
         <v>158.9</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="4" t="n">
         <v>176.7</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="n">
+      <c r="E33" s="5" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>23262</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
         <v>2022</v>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B34" s="4" t="n">
         <v>227.3</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" s="4" t="n">
         <v>167.2</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="4" t="n">
         <v>185.6</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="n">
+      <c r="E34" s="5" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>24436</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
         <v>2023</v>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="4" t="n">
         <v>236.6</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="4" t="n">
         <v>175.8</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="4" t="n">
         <v>194.4</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="n">
+      <c r="E35" s="5" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>25595</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="n">
         <v>2024</v>
       </c>
-      <c r="B36" s="3" t="n">
+      <c r="B36" s="4" t="n">
         <v>244</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C36" s="4" t="n">
         <v>178.8</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="4" t="n">
         <v>199.7</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>32</v>
+      <c r="E36" s="5" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>26287</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
